--- a/human_resources_forms/007_return_to_office_survey--human_resources_forms.xlsx
+++ b/human_resources_forms/007_return_to_office_survey--human_resources_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -803,8 +803,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -832,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'always',_'label':_'always'}</t>
+          <t>always</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'always', 'label': 'Always'}</t>
+          <t>Always</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'rarely',_'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'rarely', 'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -866,12 +866,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'occasionally',_'label':_'occasionally'}</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'occasionally', 'label': 'Occasionally'}</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'never',_'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'never', 'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -900,12 +900,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'commute_time',_'label':_'commute_time'}</t>
+          <t>commute_time</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'commute_time', 'label': 'Commute time'}</t>
+          <t>Commute time</t>
         </is>
       </c>
     </row>
@@ -917,12 +917,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'work_life_balance',_'label':_'work_life_balance'}</t>
+          <t>work_life_balance</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'work_life_balance', 'label': 'Work life balance'}</t>
+          <t>Work life balance</t>
         </is>
       </c>
     </row>
@@ -934,12 +934,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'social_interaction',_'label':_'social_interaction'}</t>
+          <t>social_interaction</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'social_interaction', 'label': 'Social interaction'}</t>
+          <t>Social interaction</t>
         </is>
       </c>
     </row>
@@ -951,12 +951,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'job_security',_'label':_'job_security'}</t>
+          <t>job_security</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'job_security', 'label': 'Job security'}</t>
+          <t>Job security</t>
         </is>
       </c>
     </row>
@@ -968,12 +968,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'personal_purpose',_'label':_'personal_purpose'}</t>
+          <t>personal_purpose</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'personal_purpose', 'label': 'Personal purpose'}</t>
+          <t>Personal purpose</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'remote',_'label':_'remote'}</t>
+          <t>remote</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'remote', 'label': 'Remote'}</t>
+          <t>Remote</t>
         </is>
       </c>
     </row>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'hybrid',_'label':_'hybrid'}</t>
+          <t>hybrid</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'hybrid', 'label': 'Hybrid'}</t>
+          <t>Hybrid</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'in_office',_'label':_'in_office'}</t>
+          <t>in_office</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'in_office', 'label': 'In office'}</t>
+          <t>In office</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'increased_productivity',_'label':_'increased_productivity'}</t>
+          <t>increased_productivity</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'increased_productivity', 'label': 'Increased productivity'}</t>
+          <t>Increased productivity</t>
         </is>
       </c>
     </row>
@@ -1053,12 +1053,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'improved_culture',_'label':_'improved_culture'}</t>
+          <t>improved_culture</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'improved_culture', 'label': 'Improved culture'}</t>
+          <t>Improved culture</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'increased_satisfaction',_'label':_'increased_satisfaction'}</t>
+          <t>increased_satisfaction</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'increased_satisfaction', 'label': 'Increased satisfaction'}</t>
+          <t>Increased satisfaction</t>
         </is>
       </c>
     </row>
@@ -1087,12 +1087,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'decreased_turnover',_'label':_'decreased_turnover'}</t>
+          <t>decreased_turnover</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'decreased_turnover', 'label': 'Decreased turnover'}</t>
+          <t>Decreased turnover</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1104,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'improved_communication',_'label':_'improved_communication'}</t>
+          <t>improved_communication</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'improved_communication', 'label': 'Improved communication'}</t>
+          <t>Improved communication</t>
         </is>
       </c>
     </row>
